--- a/Formatted.Data/cat.summary.multiple.xlsx
+++ b/Formatted.Data/cat.summary.multiple.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samanthaworthy/Documents/GitHub/Habitat_Geographic_Ranges/Formatted.Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{6E0CFE4C-1E2B-1041-9798-EDA241F82358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC01F55-FCA0-C646-9F1C-D987B6E29DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="10400" windowHeight="16480" activeTab="3" xr2:uid="{51D28AAD-446A-4643-BFD6-F30B3F59C986}"/>
+    <workbookView xWindow="380" yWindow="500" windowWidth="18500" windowHeight="16480" xr2:uid="{51D28AAD-446A-4643-BFD6-F30B3F59C986}"/>
   </bookViews>
   <sheets>
     <sheet name="cat.summary" sheetId="1" r:id="rId1"/>
@@ -18,18 +18,25 @@
     <sheet name="micro.soil" sheetId="3" r:id="rId3"/>
     <sheet name="topo.soil" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="13">
-  <si>
-    <t>Microclimate</t>
-  </si>
-  <si>
-    <t>Topography</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="10">
   <si>
     <t>Soil</t>
   </si>
@@ -55,20 +62,17 @@
     <t>Percent</t>
   </si>
   <si>
-    <t>overall.shifter</t>
+    <t>Microclim</t>
   </si>
   <si>
-    <t>generalist</t>
-  </si>
-  <si>
-    <t>overdisperse</t>
+    <t>Topo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -199,6 +203,13 @@
     <font>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -551,9 +562,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -929,104 +943,109 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7805A2-F8F7-774D-B21E-632F54F0EF10}">
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.1640625" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <f>D2/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D2/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <f>D3/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D3/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4">
-        <f>D4/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D4/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <f>D5/122</f>
-        <v>1.6393442622950821E-2</v>
+        <f>D5/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
@@ -1035,26 +1054,26 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <f>D6/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D6/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <f>D7/122</f>
-        <v>3.2786885245901641E-2</v>
+        <f>D7/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -1062,17 +1081,17 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <f>D8/122</f>
-        <v>1.6393442622950821E-2</v>
+        <f>D8/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -1080,17 +1099,17 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <f>D9/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D9/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -1098,53 +1117,53 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
         <v>5</v>
       </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <f>D10/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D10/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <f>D11/122</f>
-        <v>2.4590163934426229E-2</v>
+        <f>D11/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
         <v>5</v>
       </c>
-      <c r="C12" t="s">
-        <v>7</v>
-      </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12">
-        <f>D12/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D12/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -1155,14 +1174,14 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13">
-        <f>D13/122</f>
-        <v>2.4590163934426229E-2</v>
+        <f>D13/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -1173,14 +1192,14 @@
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14">
-        <f>D14/122</f>
-        <v>1.6393442622950821E-2</v>
+        <f>D14/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -1194,11 +1213,11 @@
         <v>5</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <f>D15/122</f>
-        <v>4.9180327868852458E-2</v>
+        <f>D15/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -1206,133 +1225,133 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <f>D16/122</f>
-        <v>1.6393442622950821E-2</v>
+        <f>D16/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <f>D17/122</f>
-        <v>3.2786885245901641E-2</v>
+        <f>D17/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <f>D18/122</f>
-        <v>4.0983606557377046E-2</v>
+        <f>D18/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <f>D19/122</f>
-        <v>1.6393442622950821E-2</v>
+        <f>D19/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <f>D20/122</f>
-        <v>9.8360655737704916E-2</v>
+        <f>D20/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <f>D21/122</f>
-        <v>1.6393442622950821E-2</v>
+        <f>D21/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22">
-        <f>D22/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D22/119*100</f>
+        <v>1.680672268907563</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -1341,453 +1360,415 @@
         <v>2</v>
       </c>
       <c r="E23">
-        <f>D23/122</f>
-        <v>1.6393442622950821E-2</v>
+        <f>D23/119*100</f>
+        <v>1.680672268907563</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D24">
         <v>2</v>
       </c>
       <c r="E24">
-        <f>D24/122</f>
-        <v>1.6393442622950821E-2</v>
+        <f>D24/119*100</f>
+        <v>1.680672268907563</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B25" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" t="s">
         <v>5</v>
       </c>
-      <c r="C25" t="s">
-        <v>6</v>
-      </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <f>D25/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D25/119*100</f>
+        <v>1.680672268907563</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D26">
         <v>2</v>
       </c>
       <c r="E26">
-        <f>D26/122</f>
-        <v>1.6393442622950821E-2</v>
+        <f>D26/119*100</f>
+        <v>1.680672268907563</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" t="s">
         <v>5</v>
       </c>
       <c r="D27">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E27">
-        <f>D27/122</f>
-        <v>0.1721311475409836</v>
+        <f>D27/119*100</f>
+        <v>1.680672268907563</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28">
-        <f>D28/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D28/119*100</f>
+        <v>1.680672268907563</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D29">
         <v>2</v>
       </c>
       <c r="E29">
-        <f>D29/122</f>
-        <v>1.6393442622950821E-2</v>
+        <f>D29/119*100</f>
+        <v>1.680672268907563</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30">
-        <f>D30/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D30/119*100</f>
+        <v>1.680672268907563</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31">
-        <f>D31/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D31/119*100</f>
+        <v>1.680672268907563</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32">
-        <f>D32/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D32/119*100</f>
+        <v>1.680672268907563</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33">
-        <f>D33/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D33/119*100</f>
+        <v>1.680672268907563</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34">
-        <f>D34/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D34/119*100</f>
+        <v>1.680672268907563</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <f>D35/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D35/119*100</f>
+        <v>1.680672268907563</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36">
-        <f>D36/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D36/119*100</f>
+        <v>2.5210084033613445</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C37" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E37">
-        <f>D37/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D37/119*100</f>
+        <v>2.5210084033613445</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B38" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38">
-        <f>D38/122</f>
-        <v>2.4590163934426229E-2</v>
+        <f>D38/119*100</f>
+        <v>3.3613445378151261</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E39">
-        <f>D39/122</f>
-        <v>1.6393442622950821E-2</v>
+        <f>D39/119*100</f>
+        <v>3.3613445378151261</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E40">
-        <f>D40/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D40/119*100</f>
+        <v>3.3613445378151261</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41">
         <v>5</v>
       </c>
-      <c r="B41" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" t="s">
-        <v>4</v>
-      </c>
-      <c r="D41">
-        <v>1</v>
-      </c>
       <c r="E41">
-        <f>D41/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D41/119*100</f>
+        <v>4.2016806722689077</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42">
         <v>5</v>
       </c>
-      <c r="B42" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" t="s">
-        <v>5</v>
-      </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
       <c r="E42">
-        <f>D42/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D42/119*100</f>
+        <v>4.2016806722689077</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C43" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E43">
-        <f>D43/122</f>
-        <v>2.4590163934426229E-2</v>
+        <f>D43/119*100</f>
+        <v>8.4033613445378155</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B44" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C44" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E44">
-        <f>D44/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>D44/119*100</f>
+        <v>10.084033613445378</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B45" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E45">
-        <f>D45/122</f>
-        <v>1.6393442622950821E-2</v>
+        <f>D45/119*100</f>
+        <v>17.647058823529413</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>5</v>
-      </c>
-      <c r="B46" t="s">
-        <v>5</v>
-      </c>
-      <c r="C46" t="s">
-        <v>5</v>
-      </c>
       <c r="D46">
-        <v>10</v>
-      </c>
-      <c r="E46">
-        <f>D46/122</f>
-        <v>8.1967213114754092E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>7</v>
-      </c>
-      <c r="B47" t="s">
-        <v>5</v>
-      </c>
-      <c r="C47" t="s">
-        <v>4</v>
-      </c>
-      <c r="D47">
-        <v>2</v>
-      </c>
-      <c r="E47">
-        <f>D47/122</f>
-        <v>1.6393442622950821E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D48">
-        <f>SUM(D2:D47)</f>
-        <v>122</v>
+        <f>SUM(D2:D45)</f>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E48">
-    <sortCondition ref="A2:A48"/>
-    <sortCondition ref="B2:B48"/>
-    <sortCondition ref="C2:C48"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E46">
+    <sortCondition ref="E2:E46"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1795,295 +1776,263 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E46A41F1-13BA-3347-A18C-70D869C0F09F}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="10.83203125" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>4</v>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>5</v>
-      </c>
-      <c r="D2">
-        <f>C2/122</f>
-        <v>4.0983606557377046E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="C2" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2">
+        <f>C2/119*100</f>
+        <v>3.3613445378151261</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <f>C3/122</f>
-        <v>4.0983606557377046E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>4</v>
+        <v>4</v>
+      </c>
+      <c r="C3" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2">
+        <f>C3/119*100</f>
+        <v>3.3613445378151261</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>8</v>
-      </c>
-      <c r="D4">
-        <f>C4/122</f>
-        <v>6.5573770491803282E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="C4" s="2">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2">
+        <f>C4/119*100</f>
+        <v>7.5630252100840334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1">
+        <f>C5/119*100</f>
+        <v>2.5210084033613445</v>
+      </c>
+      <c r="F5" s="1">
+        <f>SUM(C5:C8,C12:C14)</f>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1">
         <v>13</v>
       </c>
-      <c r="D5">
-        <f>C5/122</f>
-        <v>0.10655737704918032</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="1">
+      <c r="D6" s="1">
+        <f>C6/119*100</f>
+        <v>10.92436974789916</v>
+      </c>
+      <c r="F6" s="1">
+        <f>F5/119*100</f>
+        <v>73.109243697478988</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1">
         <v>25</v>
       </c>
-      <c r="D6">
-        <f>C6/122</f>
-        <v>0.20491803278688525</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="1">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <f>C7/122</f>
-        <v>2.4590163934426229E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
+      <c r="D7" s="1">
+        <f>C7/119*100</f>
+        <v>21.008403361344538</v>
+      </c>
+      <c r="F7" s="1">
+        <f>SUM(C7,C8,C13,C14)</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C8" s="1">
         <v>27</v>
       </c>
-      <c r="D8">
-        <f>C8/122</f>
-        <v>0.22131147540983606</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>8</v>
+      <c r="D8" s="1">
+        <f>C8/119*100</f>
+        <v>22.689075630252102</v>
+      </c>
+      <c r="F8" s="1">
+        <f>70/87*100</f>
+        <v>80.459770114942529</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2">
+        <f>C9/119*100</f>
+        <v>2.5210084033613445</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="2">
         <v>5</v>
       </c>
-      <c r="D9">
-        <f>C9/122</f>
-        <v>4.0983606557377046E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <f>C10/122</f>
-        <v>2.4590163934426229E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>8</v>
+      <c r="D10" s="2">
+        <f>C10/119*100</f>
+        <v>4.2016806722689077</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-      <c r="D11">
-        <f>C11/122</f>
-        <v>5.737704918032787E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>6</v>
+      </c>
+      <c r="D11" s="2">
+        <f>C11/119*100</f>
+        <v>5.0420168067226889</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
       </c>
-      <c r="D12">
-        <f>C12/122</f>
-        <v>8.1967213114754103E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>5</v>
+      <c r="D12" s="1">
+        <f>C12/119*100</f>
+        <v>0.84033613445378152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C13" s="1">
         <v>2</v>
       </c>
-      <c r="D13">
-        <f>C13/122</f>
-        <v>1.6393442622950821E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>5</v>
+      <c r="D13" s="1">
+        <f>C13/119*100</f>
+        <v>1.680672268907563</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C14" s="1">
         <v>16</v>
       </c>
-      <c r="D14">
-        <f>C14/122</f>
-        <v>0.13114754098360656</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>7</v>
+      <c r="D14" s="1">
+        <f>C14/119*100</f>
+        <v>13.445378151260504</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-      <c r="D15">
-        <f>C15/122</f>
-        <v>1.6393442622950821E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2">
+        <f>C15/119*100</f>
+        <v>0.84033613445378152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C16" s="2">
         <f>SUM(C2:C15)</f>
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19">
-        <f>25+27+16+2</f>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C21">
-        <f>SUM(C18:C20)</f>
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C22">
-        <f>C21/122</f>
-        <v>0.71311475409836067</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C23">
-        <f>70/87</f>
-        <v>0.8045977011494253</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D16">
     <sortCondition ref="A2:A16"/>
-    <sortCondition ref="B2:B16"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2091,333 +2040,320 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D920D12-40C2-1744-B5D4-157087F512B4}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>4</v>
+      <c r="A2" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <f>C2/122</f>
-        <v>3.2786885245901641E-2</v>
+        <f>C2/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>4</v>
+      <c r="A3" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <f>C3/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>C3/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>4</v>
+      <c r="A4" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <f>C4/122</f>
-        <v>1.6393442622950821E-2</v>
+        <f>C4/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>4</v>
+      <c r="A5" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <f>C5/122</f>
-        <v>6.5573770491803282E-2</v>
+        <f>C5/119*100</f>
+        <v>1.680672268907563</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>4</v>
+      <c r="A6" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <f>C6/122</f>
-        <v>2.4590163934426229E-2</v>
+        <f>C6/119*100</f>
+        <v>1.680672268907563</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>6</v>
+      <c r="A7" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <f>C7/122</f>
-        <v>7.3770491803278687E-2</v>
+        <f>C7/119*100</f>
+        <v>1.680672268907563</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>6</v>
+      <c r="A8" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <f>C8/122</f>
-        <v>5.737704918032787E-2</v>
+        <f>C8/119*100</f>
+        <v>2.5210084033613445</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <f>C9/122</f>
-        <v>4.9180327868852458E-2</v>
+        <f>C9/119*100</f>
+        <v>2.5210084033613445</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>6</v>
+      <c r="A10" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="B10" t="s">
         <v>5</v>
       </c>
       <c r="C10">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <f>C10/122</f>
-        <v>0.33606557377049179</v>
+        <f>C10/119*100</f>
+        <v>3.3613445378151261</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <f>C11/119*100</f>
+        <v>3.3613445378151261</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12">
+        <f>C12/119*100</f>
+        <v>3.3613445378151261</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <f>C13/119*100</f>
+        <v>4.2016806722689077</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <f>C14/119*100</f>
+        <v>4.2016806722689077</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+      <c r="D15">
+        <f>C15/119*100</f>
+        <v>5.0420168067226889</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16">
         <v>7</v>
       </c>
-      <c r="C11">
-        <v>5</v>
-      </c>
-      <c r="D11">
-        <f>C11/122</f>
-        <v>4.0983606557377046E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12">
-        <f>C12/122</f>
-        <v>2.4590163934426229E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <f>C13/122</f>
-        <v>8.1967213114754103E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14">
-        <f>C14/122</f>
-        <v>1.6393442622950821E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15">
-        <v>5</v>
-      </c>
-      <c r="D15">
-        <f>C15/122</f>
-        <v>4.0983606557377046E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="D16">
+        <f>C16/119*100</f>
+        <v>5.8823529411764701</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17">
         <v>7</v>
       </c>
-      <c r="C16">
-        <v>4</v>
-      </c>
-      <c r="D16">
-        <f>C16/122</f>
-        <v>3.2786885245901641E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17">
-        <v>4</v>
-      </c>
       <c r="D17">
-        <f>C17/122</f>
-        <v>3.2786885245901641E-2</v>
+        <f>C17/119*100</f>
+        <v>5.8823529411764701</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>5</v>
+      <c r="A18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D18">
-        <f>C18/122</f>
-        <v>8.1967213114754103E-3</v>
+        <f>C18/119*100</f>
+        <v>8.4033613445378155</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>5</v>
+      <c r="A19" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D19">
-        <f>C19/122</f>
-        <v>1.6393442622950821E-2</v>
+        <f>C19/119*100</f>
+        <v>10.084033613445378</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>5</v>
+      <c r="A20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="D20">
-        <f>C20/122</f>
-        <v>9.8360655737704916E-2</v>
+        <f>C20/119*100</f>
+        <v>33.613445378151262</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" t="s">
-        <v>4</v>
-      </c>
       <c r="C21">
-        <v>2</v>
-      </c>
-      <c r="D21">
-        <f>C21/122</f>
-        <v>1.6393442622950821E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C22">
-        <f>SUM(C2:C21)</f>
-        <v>122</v>
+        <f>SUM(C2:C20)</f>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D22">
-    <sortCondition ref="A2:A22"/>
-    <sortCondition ref="B2:B22"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D21">
+    <sortCondition ref="D2:D21"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2427,271 +2363,274 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB6A83E8-C3A8-BF43-8764-DF1790C709C4}">
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
+      <c r="A1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <f>C2/122</f>
-        <v>4.9180327868852458E-2</v>
+        <f>C2/119*100</f>
+        <v>0.84033613445378152</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <f>C3/119*100</f>
+        <v>1.680672268907563</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <f>C4/119*100</f>
+        <v>2.5210084033613445</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <f>C5/119*100</f>
+        <v>2.5210084033613445</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <f>C6/119*100</f>
+        <v>2.5210084033613445</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <f>C7/119*100</f>
+        <v>3.3613445378151261</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <f>C8/119*100</f>
+        <v>4.2016806722689077</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <f>C9/119*100</f>
+        <v>4.2016806722689077</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <f>C10/119*100</f>
+        <v>4.2016806722689077</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11">
+        <f>C11/119*100</f>
+        <v>4.2016806722689077</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12">
+        <f>C12/119*100</f>
+        <v>5.0420168067226889</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="D13">
+        <f>C13/119*100</f>
+        <v>5.8823529411764701</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14">
         <v>8</v>
       </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <f>C3/122</f>
-        <v>3.2786885245901641E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>9</v>
-      </c>
-      <c r="D4">
-        <f>C4/122</f>
-        <v>7.3770491803278687E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <f>C5/122</f>
-        <v>4.0983606557377046E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <f>C6/122</f>
-        <v>4.9180327868852458E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <f>C7/122</f>
-        <v>4.0983606557377046E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="D14">
+        <f>C14/119*100</f>
+        <v>6.7226890756302522</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15">
         <v>8</v>
       </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8">
-        <f>C8/122</f>
-        <v>2.4590163934426229E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9">
-        <v>18</v>
-      </c>
-      <c r="D9">
-        <f>C9/122</f>
-        <v>0.14754098360655737</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <f>C10/122</f>
-        <v>2.4590163934426229E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <f>C11/122</f>
-        <v>8.1967213114754103E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12">
-        <f>C12/122</f>
-        <v>1.6393442622950821E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13">
-        <v>10</v>
-      </c>
-      <c r="D13">
-        <f>C13/122</f>
-        <v>8.1967213114754092E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>4</v>
-      </c>
-      <c r="D14">
-        <f>C14/122</f>
-        <v>3.2786885245901641E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15">
-        <v>5</v>
-      </c>
       <c r="D15">
-        <f>C15/122</f>
-        <v>4.0983606557377046E-2</v>
+        <f>C15/119*100</f>
+        <v>6.7226890756302522</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" t="s">
-        <v>5</v>
+      <c r="A16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="C16">
+        <v>17</v>
+      </c>
+      <c r="D16">
+        <f>C16/119*100</f>
+        <v>14.285714285714285</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17">
         <v>37</v>
       </c>
-      <c r="D16">
-        <f>C16/122</f>
-        <v>0.30327868852459017</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17">
-        <v>4</v>
-      </c>
       <c r="D17">
-        <f>C17/122</f>
-        <v>3.2786885245901641E-2</v>
+        <f>C17/119*100</f>
+        <v>31.092436974789916</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="3"/>
       <c r="C18">
         <f>SUM(C2:C17)</f>
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D18">
-    <sortCondition ref="A2:A18"/>
-    <sortCondition ref="B2:B18"/>
+    <sortCondition ref="D2:D18"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
